--- a/etf_holdings/2026-10-27_00400A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-27_00400A_full_holdings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-27 22:43:16</t>
+          <t>2026-10-27 22:55:45</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-27 22:43:16</t>
+          <t>2026-10-27 22:55:45</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27 22:43:16</t>
+          <t>2026-10-27 22:55:45</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-27 22:43:16</t>
+          <t>2026-10-27 22:55:45</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-27 22:43:16</t>
+          <t>2026-10-27 22:55:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-27 22:43:16</t>
+          <t>2026-10-27 22:55:45</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-27 22:43:16</t>
+          <t>2026-10-27 22:55:45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-27 22:43:16</t>
+          <t>2026-10-27 22:55:45</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-27 22:43:16</t>
+          <t>2026-10-27 22:55:45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-27 22:43:16</t>
+          <t>2026-10-27 22:55:45</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-27 22:43:16</t>
+          <t>2026-10-27 22:55:45</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-27 22:43:16</t>
+          <t>2026-10-27 22:55:45</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-27 22:43:16</t>
+          <t>2026-10-27 22:55:45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-27 22:43:16</t>
+          <t>2026-10-27 22:55:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-27 22:43:16</t>
+          <t>2026-10-27 22:55:45</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1393,6 +1393,2324 @@
         </is>
       </c>
       <c r="M16" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-10-27 22:55:46</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>3044健鼎</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-6.12%522</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-6.12%</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>522</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2.24%1,287,000</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2.24%</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>1287000</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>-0.14%</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-10-27 22:55:46</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>3661世芯-KY</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0%3495</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>3495</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2.14%184,000</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2.14%</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>184000</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-10-27 22:55:46</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2303聯電</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-2.39%122.5</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-2.39%</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1.71%4,192,000</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>1.71%</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>4192000</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>-0.04%</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-10-27 22:55:46</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2881富邦金</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>+2.21%162</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>+2.21%</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>162</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1.68%3,104,000</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1.68%</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>3104000</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>+0.04%</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-10-27 22:55:46</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2891中信金</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>+0.13%75</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>+0.13%</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>75</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1.64%6,547,000</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>1.64%</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>6547000</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-10-27 22:55:46</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2603長榮</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>+0.58%261.5</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>+0.58%</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>261.5</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1.63%1,871,000</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>1.63%</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>1871000</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-10-27 22:55:46</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>3036文曄</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>+0.94%215</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>+0.94%</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>215</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1.58%2,208,000</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>1.58%</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>2208000</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-10-27 22:55:46</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>6505台塑化</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>-0.47%106</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-0.47%</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>106</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1.53%4,327,000</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>1.53%</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>4327000</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-10-27 22:55:46</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>3008大立光</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-2.83%6000</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-2.83%</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1.52%76,000</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>1.52%</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>76000</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>-0.04%</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-10-27 22:55:46</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>5274信驊</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>+0.03%16015</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>+0.03%</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>16015</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1.52%28,400</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>1.52%</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>28400</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-10-27 22:55:46</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2345智邦</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>-0.85%1760</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-0.85%</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>1760</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1.48%252,000</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>1.48%</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>252000</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-10-27 22:55:46</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>3665貿聯-KY</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>-7.47%1735</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-7.47%</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>1735</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1.32%228,000</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>1.32%</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>228000</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>-0.10%</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-10-27 22:55:46</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2327國巨*</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>+2.76%521</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>+2.76%</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>521</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1.23%708,000</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>1.23%</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>708000</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>+0.03%</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-10-27 22:55:46</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>3529力旺</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>+1.21%2515</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>+1.21%</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>2515</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1.19%142,000</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>1.19%</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>142000</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-10-27 22:55:46</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>6274台燿</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>-9.86%1280</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-9.86%</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>1280</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1.19%279,000</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>1.19%</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>279000</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>-0.13%</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-10-27 22:55:48</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>3</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>6187萬潤</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>+1.98%1285</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>+1.98%</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>1285</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1.07%249,000</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>1.07%</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>249000</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-10-27 22:55:48</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>3231緯創</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>+0.26%190.5</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>+0.26%</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>190.5</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1.03%1,614,000</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>1.03%</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>1614000</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-10-27 22:55:48</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>3711日月光投控</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>-0.46%651</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-0.46%</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>651</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1.01%464,000</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>1.01%</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>464000</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-10-27 22:55:48</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>3</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>3406玉晶光</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>+4.31%1210</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>+4.31%</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>1210</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>0.99%245,000</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>0.99%</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>245000</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>+0.04%</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-10-27 22:55:48</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>3533嘉澤</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>+7.24%1925</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>+7.24%</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>1925</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>0.98%152,000</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>0.98%</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>152000</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>+0.07%</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-10-27 22:55:48</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>3</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2449京元電子</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>+2.48%269</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>+2.48%</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>269</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>0.90%999,000</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>0.90%</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>999000</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-10-27 22:55:48</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>3</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>6147頎邦</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>+1.97%207</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>+1.97%</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>207</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>0.89%1,293,000</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>0.89%</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>1293000</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-10-27 22:55:48</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>3</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>7750新代</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>+9.94%1990</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>+9.94%</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>1990</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>0.81%122,000</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>0.81%</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>122000</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>+0.07%</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-10-27 22:55:48</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>3</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2313華通</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>-3.79%216</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-3.79%</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>216</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>0.80%1,107,336</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>0.80%</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>1107336</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>-0.03%</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-10-27 22:55:48</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>3</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2317鴻海</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>+1.02%247.5</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>+1.02%</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>247.5</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>0.79%960,000</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>0.79%</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>960000</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-10-27 22:55:48</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>3</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>7769鴻勁</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>-1.23%5210</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-1.23%</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>5210</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>0.70%40,000</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>0.70%</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>40000</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-10-27 22:55:48</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>3</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>3081聯亞</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>+5.26%2500</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>+5.26%</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>2500</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>0.68%82,000</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>0.68%</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>82000</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>+0.03%</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-10-27 22:55:48</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>3</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2637慧洋-KY</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>0%100.5</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>0.48%1,424,000</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>0.48%</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>1424000</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-10-27 22:55:48</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>3</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>4958臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>-8.29%520</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-8.29%</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>520</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>0.45%257,000</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>0.45%</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>257000</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>-0.04%</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-10-27 22:55:48</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>3</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>3167大量</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>+3.9%960</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>+3.9%</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>960</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>0.37%115,000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>0.37%</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>115000</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-10-27 22:55:49</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>4</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>5434崇越</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>-0.73%546</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-0.73%</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>546</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.36%200,000</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.36%</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>200000</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-10-27 22:55:49</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>4</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>3293鈊象</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>+1.14%796</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>+1.14%</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>796</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.35%133,000</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.35%</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>133000</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-10-27 22:55:49</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>4</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>3090日電貿</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>-2.24%153</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-2.24%</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>153</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.30%592,000</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.30%</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>592000</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-10-27 22:55:49</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>4</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>6271同欣電</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>-3.49%207.5</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-3.49%</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>207.5</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.24%340,000</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.24%</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>340000</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-10-27 22:55:49</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>4</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>6121新普</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>+3.02%375</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>+3.02%</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>375</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.22%178,000</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.22%</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>178000</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-10-27 22:55:49</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>4</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>9939宏全</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>+0.39%127.5</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>+0.39%</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>127.5</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.08%180,000</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.08%</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>180000</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-10-27 22:55:49</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>4</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1476儒鴻</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>-0.46%323</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-0.46%</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>323</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>0.08%70,000</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>0.08%</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>70000</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-10-27 22:55:49</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>4</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>1215卜蜂</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>+1.87%109</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>+1.87%</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>109</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>0.07%200,000</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>0.07%</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>200000</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
         <is>
           <t>登入查看</t>
         </is>

--- a/etf_holdings/2026-10-27_00400A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-27_00400A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:45</t>
+          <t>2026-10-27 23:24:57</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:45</t>
+          <t>2026-10-27 23:24:57</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:45</t>
+          <t>2026-10-27 23:24:57</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:45</t>
+          <t>2026-10-27 23:24:57</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:45</t>
+          <t>2026-10-27 23:24:57</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:45</t>
+          <t>2026-10-27 23:24:57</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:45</t>
+          <t>2026-10-27 23:24:57</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:45</t>
+          <t>2026-10-27 23:24:57</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:45</t>
+          <t>2026-10-27 23:24:57</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:45</t>
+          <t>2026-10-27 23:24:57</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:45</t>
+          <t>2026-10-27 23:24:57</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:45</t>
+          <t>2026-10-27 23:24:57</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:45</t>
+          <t>2026-10-27 23:24:57</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:45</t>
+          <t>2026-10-27 23:24:57</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:45</t>
+          <t>2026-10-27 23:24:57</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:46</t>
+          <t>2026-10-27 23:24:58</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:46</t>
+          <t>2026-10-27 23:24:58</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:46</t>
+          <t>2026-10-27 23:24:58</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:46</t>
+          <t>2026-10-27 23:24:58</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:46</t>
+          <t>2026-10-27 23:24:58</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:46</t>
+          <t>2026-10-27 23:24:58</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:46</t>
+          <t>2026-10-27 23:24:58</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:46</t>
+          <t>2026-10-27 23:24:58</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:46</t>
+          <t>2026-10-27 23:24:58</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:46</t>
+          <t>2026-10-27 23:24:58</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:46</t>
+          <t>2026-10-27 23:24:58</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:46</t>
+          <t>2026-10-27 23:24:58</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:46</t>
+          <t>2026-10-27 23:24:58</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:46</t>
+          <t>2026-10-27 23:24:58</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:46</t>
+          <t>2026-10-27 23:24:58</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:48</t>
+          <t>2026-10-27 23:25:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:48</t>
+          <t>2026-10-27 23:25:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:48</t>
+          <t>2026-10-27 23:25:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:48</t>
+          <t>2026-10-27 23:25:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:48</t>
+          <t>2026-10-27 23:25:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:48</t>
+          <t>2026-10-27 23:25:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:48</t>
+          <t>2026-10-27 23:25:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:48</t>
+          <t>2026-10-27 23:25:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:48</t>
+          <t>2026-10-27 23:25:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:48</t>
+          <t>2026-10-27 23:25:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:48</t>
+          <t>2026-10-27 23:25:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:48</t>
+          <t>2026-10-27 23:25:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:48</t>
+          <t>2026-10-27 23:25:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:48</t>
+          <t>2026-10-27 23:25:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:48</t>
+          <t>2026-10-27 23:25:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:49</t>
+          <t>2026-10-27 23:25:01</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:49</t>
+          <t>2026-10-27 23:25:01</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:49</t>
+          <t>2026-10-27 23:25:01</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:49</t>
+          <t>2026-10-27 23:25:01</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:49</t>
+          <t>2026-10-27 23:25:01</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:49</t>
+          <t>2026-10-27 23:25:01</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:49</t>
+          <t>2026-10-27 23:25:01</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-10-27 22:55:49</t>
+          <t>2026-10-27 23:25:01</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
